--- a/docs/harness/wirelist/CabinPower-wirelist.xlsx
+++ b/docs/harness/wirelist/CabinPower-wirelist.xlsx
@@ -2225,7 +2225,7 @@
       <c r="AD12" s="54" t="inlineStr"/>
       <c r="AE12" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS1-2 (14 AWG); splice sp_hl named in SoT</t>
+          <t>fuse-box plan fb_logic BUS1-2 (14 AWG); splice sp_hl: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF12" s="54" t="inlineStr">
@@ -2338,12 +2338,12 @@
       <c r="AD13" s="38" t="inlineStr"/>
       <c r="AE13" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS1-3 (14 AWG)</t>
+          <t>fuse-box plan fb_logic BUS1-3 (14 AWG); splice sp_hr: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF13" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_hr is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG13" s="38" t="inlineStr"/>
@@ -2451,12 +2451,12 @@
       <c r="AD14" s="54" t="inlineStr"/>
       <c r="AE14" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS1-4 (14 AWG)</t>
+          <t>fuse-box plan fb_logic BUS1-4 (14 AWG); splice sp_hz: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF14" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_hz is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG14" s="54" t="inlineStr"/>
@@ -2570,12 +2570,12 @@
       <c r="AD15" s="38" t="inlineStr"/>
       <c r="AE15" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS1-7 (20 AWG)</t>
+          <t>fuse-box plan fb_logic BUS1-7 (20 AWG); splice sp_at_12v: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF15" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_at_12v is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG15" s="38" t="inlineStr">
@@ -2693,12 +2693,12 @@
       <c r="AD16" s="54" t="inlineStr"/>
       <c r="AE16" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS1-8 (20 AWG)</t>
+          <t>fuse-box plan fb_logic BUS1-8 (20 AWG); splice sp_12v_shk: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF16" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_12v_shk is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG16" s="54" t="inlineStr">
@@ -3308,7 +3308,7 @@
       <c r="AD21" s="38" t="inlineStr"/>
       <c r="AE21" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-6 (16 AWG); splice sp_dev named in SoT</t>
+          <t>fuse-box plan fb_logic BUS2-6 (16 AWG); splice sp_dev: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF21" s="38" t="inlineStr">
@@ -3657,12 +3657,12 @@
       <c r="AD24" s="54" t="inlineStr"/>
       <c r="AE24" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-9 (20 AWG)</t>
+          <t>fuse-box plan fb_logic BUS2-9 (20 AWG); splice sp_ig: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF24" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_ig is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG24" s="54" t="inlineStr">
@@ -5408,7 +5408,7 @@
       <c r="AD39" s="38" t="inlineStr"/>
       <c r="AE39" s="38" t="inlineStr">
         <is>
-          <t>channels.csv k_hl c2 Coil 85 (HEAD_RLY); fuse-box plan k_hl 85 (18 AWG); splice sp_head_coil named in SoT</t>
+          <t>channels.csv k_hl c2 Coil 85 (HEAD_RLY); fuse-box plan k_hl 85 (18 AWG); splice sp_head_coil: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF39" s="38" t="inlineStr">
@@ -5652,12 +5652,12 @@
       <c r="AD41" s="38" t="inlineStr"/>
       <c r="AE41" s="38" t="inlineStr">
         <is>
-          <t>channels.csv k_horn c4 Contact 87 (HORN); fuse-box plan k_horn 87 (14 AWG)</t>
+          <t>channels.csv k_horn c4 Contact 87 (HORN); fuse-box plan k_horn 87 (14 AWG); splice sp_horn: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF41" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_horn is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG41" s="38" t="inlineStr">
@@ -5767,7 +5767,7 @@
       <c r="AD42" s="54" t="inlineStr"/>
       <c r="AE42" s="54" t="inlineStr">
         <is>
-          <t>channels.csv k_hr c2 Coil 85 (HEAD_RLY); fuse-box plan k_hr 85 (18 AWG); splice sp_head_coil named in SoT</t>
+          <t>channels.csv k_hr c2 Coil 85 (HEAD_RLY); fuse-box plan k_hr 85 (18 AWG); splice sp_head_coil: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF42" s="54" t="inlineStr">
@@ -5878,12 +5878,12 @@
       <c r="AD43" s="38" t="inlineStr"/>
       <c r="AE43" s="38" t="inlineStr">
         <is>
-          <t>channels.csv k_htr c1 Coil 30 (BLOWER); fuse-box plan k_htr 30 (8 AWG)</t>
+          <t>channels.csv k_htr c1 Coil 30 (BLOWER); fuse-box plan k_htr 30 (8 AWG); splice sp_htr87: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF43" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_htr87 is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG43" s="38" t="inlineStr"/>
@@ -6118,12 +6118,12 @@
       <c r="AD45" s="38" t="inlineStr"/>
       <c r="AE45" s="38" t="inlineStr">
         <is>
-          <t>channels.csv k_htr c5 Contact 87a (CHASSIS_CAB); fuse-box plan k_htr 87a (14 AWG)</t>
+          <t>channels.csv k_htr c5 Contact 87a (CHASSIS_CAB); fuse-box plan k_htr 87a (14 AWG); end t_pdb_gnd_htr: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF45" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_pdb_gnd_htr (POWER box NEG bar M8 stud (glove box)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG45" s="38" t="inlineStr"/>
@@ -6227,12 +6227,12 @@
       <c r="AD46" s="54" t="inlineStr"/>
       <c r="AE46" s="54" t="inlineStr">
         <is>
-          <t>channels.csv k_pwr c2 Coil 85 (CHASSIS_CAB); fuse-box plan k_pwr 85 (18 AWG)</t>
+          <t>channels.csv k_pwr c2 Coil 85 (CHASSIS_CAB); fuse-box plan k_pwr 85 (18 AWG); end t_pdb_gnd_pwr: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF46" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_pdb_gnd_pwr (POWER box NEG bar M8 stud (glove box)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG46" s="54" t="inlineStr"/>
@@ -6336,12 +6336,12 @@
       <c r="AD47" s="38" t="inlineStr"/>
       <c r="AE47" s="38" t="inlineStr">
         <is>
-          <t>channels.csv k_rev c2 Coil 85 (CHASSIS_CAB); fuse-box plan k_rev 85 (20 AWG)</t>
+          <t>channels.csv k_rev c2 Coil 85 (CHASSIS_CAB); fuse-box plan k_rev 85 (20 AWG); end t_pdb_gnd_rev: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF47" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_pdb_gnd_rev (POWER box NEG bar M8 stud (glove box)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG47" s="38" t="inlineStr"/>
@@ -6457,7 +6457,7 @@
       <c r="AD48" s="54" t="inlineStr"/>
       <c r="AE48" s="54" t="inlineStr">
         <is>
-          <t>channels.csv k_rev c4 Contact 87 (REV_LAMP); fuse-box plan k_rev 87 (16 AWG); splice sp_rl_rev named in SoT</t>
+          <t>channels.csv k_rev c4 Contact 87 (REV_LAMP); fuse-box plan k_rev 87 (16 AWG); splice sp_rl_rev: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF48" s="54" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="AE49" s="38" t="inlineStr">
         <is>
-          <t>flying lead FL_OEM_JB3_B9: EWD J/B3 pin 3B-9 R-L</t>
+          <t>flying lead FL_OEM_JB3_B9: EWD J/B3 pin 3B-9 R-L; splice sp_rev_gauge: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF49" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_rev_gauge is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG49" s="38" t="inlineStr"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="AE53" s="38" t="inlineStr">
         <is>
-          <t>splice sp_head_coil named in SoT; flying lead FL_OEM_IE1_C2: EWD IE1 pin 2 R-Y</t>
+          <t>splice sp_head_coil: node of the wire list (SoT); flying lead FL_OEM_IE1_C2: EWD IE1 pin 2 R-Y</t>
         </is>
       </c>
       <c r="AF53" s="38" t="inlineStr">
@@ -7227,7 +7227,7 @@
       <c r="AD54" s="54" t="inlineStr"/>
       <c r="AE54" s="54" t="inlineStr">
         <is>
-          <t>splice sp_hl named in SoT; channels.csv k_hl c1 Coil 30 (FB_HL); fuse-box plan k_hl 30 (14 AWG)</t>
+          <t>splice sp_hl: node of the wire list (SoT); channels.csv k_hl c1 Coil 30 (FB_HL); fuse-box plan k_hl 30 (14 AWG)</t>
         </is>
       </c>
       <c r="AF54" s="54" t="inlineStr">
@@ -7338,7 +7338,7 @@
       <c r="AD55" s="38" t="inlineStr"/>
       <c r="AE55" s="38" t="inlineStr">
         <is>
-          <t>splice sp_hl named in SoT; channels.csv k_hl c3 Coil 86 (FB_HL); fuse-box plan k_hl 86 (16 AWG)</t>
+          <t>splice sp_hl: node of the wire list (SoT); channels.csv k_hl c3 Coil 86 (FB_HL); fuse-box plan k_hl 86 (16 AWG)</t>
         </is>
       </c>
       <c r="AF55" s="38" t="inlineStr">
@@ -7449,12 +7449,12 @@
       <c r="AD56" s="54" t="inlineStr"/>
       <c r="AE56" s="54" t="inlineStr">
         <is>
-          <t>channels.csv k_hr c1 Coil 30 (FB_HR); fuse-box plan k_hr 30 (14 AWG)</t>
+          <t>splice sp_hr: node of the wire list (SoT); channels.csv k_hr c1 Coil 30 (FB_HR); fuse-box plan k_hr 30 (14 AWG)</t>
         </is>
       </c>
       <c r="AF56" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_hr is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG56" s="54" t="inlineStr"/>
@@ -7560,12 +7560,12 @@
       <c r="AD57" s="38" t="inlineStr"/>
       <c r="AE57" s="38" t="inlineStr">
         <is>
-          <t>channels.csv k_hr c3 Coil 86 (FB_HR); fuse-box plan k_hr 86 (16 AWG)</t>
+          <t>splice sp_hr: node of the wire list (SoT); channels.csv k_hr c3 Coil 86 (FB_HR); fuse-box plan k_hr 86 (16 AWG)</t>
         </is>
       </c>
       <c r="AF57" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_hr is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG57" s="38" t="inlineStr"/>
@@ -7691,12 +7691,12 @@
       </c>
       <c r="AE58" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_B4_C2: EWD B4 pin 2 B (black)</t>
+          <t>splice sp_htr87: node of the wire list (SoT); flying lead FL_B4_C2: EWD B4 pin 2 B (black)</t>
         </is>
       </c>
       <c r="AF58" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_htr87 is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG58" s="54" t="inlineStr">
@@ -7808,12 +7808,12 @@
       <c r="AD59" s="38" t="inlineStr"/>
       <c r="AE59" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_power ACPS IN (14 AWG)</t>
+          <t>splice sp_htr87: node of the wire list (SoT); fuse-box plan fb_power ACPS IN (14 AWG)</t>
         </is>
       </c>
       <c r="AF59" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_htr87 is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG59" s="38" t="inlineStr"/>
@@ -7939,12 +7939,12 @@
       </c>
       <c r="AE60" s="54" t="inlineStr">
         <is>
-          <t>flying lead FL_OEM_IE1_C12: EWD IE1 pin 12 W</t>
+          <t>splice sp_hz: node of the wire list (SoT); flying lead FL_OEM_IE1_C12: EWD IE1 pin 12 W</t>
         </is>
       </c>
       <c r="AF60" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_hz is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG60" s="54" t="inlineStr">
@@ -8054,12 +8054,12 @@
       <c r="AD61" s="38" t="inlineStr"/>
       <c r="AE61" s="38" t="inlineStr">
         <is>
-          <t>channels.csv k_horn c1 Coil 30 (FB_HZ); fuse-box plan k_horn 30 (16 AWG)</t>
+          <t>splice sp_hz: node of the wire list (SoT); channels.csv k_horn c1 Coil 30 (FB_HZ); fuse-box plan k_horn 30 (16 AWG)</t>
         </is>
       </c>
       <c r="AF61" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_hz is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG61" s="38" t="inlineStr"/>
@@ -8165,12 +8165,12 @@
       <c r="AD62" s="54" t="inlineStr"/>
       <c r="AE62" s="54" t="inlineStr">
         <is>
-          <t>channels.csv k_horn c3 Coil 86 (FB_HZ); fuse-box plan k_horn 86 (16 AWG)</t>
+          <t>splice sp_hz: node of the wire list (SoT); channels.csv k_horn c3 Coil 86 (FB_HZ); fuse-box plan k_horn 86 (16 AWG)</t>
         </is>
       </c>
       <c r="AF62" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_hz is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG62" s="54" t="inlineStr"/>
@@ -8280,12 +8280,12 @@
       <c r="AD63" s="38" t="inlineStr"/>
       <c r="AE63" s="38" t="inlineStr">
         <is>
-          <t>channels.csv k_rev c1 Coil 30 (GAUGE_REV); fuse-box plan k_rev 30 (16 AWG)</t>
+          <t>splice sp_rev_gauge: node of the wire list (SoT); channels.csv k_rev c1 Coil 30 (GAUGE_REV); fuse-box plan k_rev 30 (16 AWG)</t>
         </is>
       </c>
       <c r="AF63" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_rev_gauge is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG63" s="38" t="inlineStr"/>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="L3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="L4" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="L5" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="L6" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="L7" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="L8" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/CabinPower-wirelist.xlsx
+++ b/docs/harness/wirelist/CabinPower-wirelist.xlsx
@@ -1970,7 +1970,7 @@
       </c>
       <c r="R10" s="47" t="inlineStr">
         <is>
-          <t>+12V EFI86 5A (LOGIC BUS1-1)</t>
+          <t>+12V EFI relay coil+ (LOGIC BUS1-1)</t>
         </is>
       </c>
       <c r="S10" s="48" t="inlineStr"/>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="R11" s="31" t="inlineStr">
         <is>
-          <t>+12V ETB 10A (LOGIC BUS1-10)</t>
+          <t>+12V ETB relay +12 V in (LOGIC BUS1-10)</t>
         </is>
       </c>
       <c r="S11" s="32" t="inlineStr"/>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="R12" s="47" t="inlineStr">
         <is>
-          <t>+12V HL 15A (LOGIC BUS1-2)</t>
+          <t>+12V Head LH +12 V feed (LOGIC BUS1-2)</t>
         </is>
       </c>
       <c r="S12" s="48" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="R13" s="31" t="inlineStr">
         <is>
-          <t>+12V HR 15A (LOGIC BUS1-3)</t>
+          <t>+12V Head RH +12 V feed (LOGIC BUS1-3)</t>
         </is>
       </c>
       <c r="S13" s="32" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="R14" s="47" t="inlineStr">
         <is>
-          <t>+12V HZ 15A (LOGIC BUS1-4)</t>
+          <t>+12V Haz-horn +12 V feed (LOGIC BUS1-4)</t>
         </is>
       </c>
       <c r="S14" s="48" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="R15" s="31" t="inlineStr">
         <is>
-          <t>+12V ALM 5A (LOGIC BUS1-7)</t>
+          <t>+12V Alarm +12 V (LOGIC BUS1-7)</t>
         </is>
       </c>
       <c r="S15" s="32" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="R16" s="47" t="inlineStr">
         <is>
-          <t>+12V ALMS 2A (LOGIC BUS1-8)</t>
+          <t>+12V Shock sensor +12 V (LOGIC BUS1-8)</t>
         </is>
       </c>
       <c r="S16" s="48" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R17" s="31" t="inlineStr">
         <is>
-          <t>+12V LAM 7.5A (LOGIC BUS2-1)</t>
+          <t>+12V CAN-Lambda +12 V (LOGIC BUS2-1)</t>
         </is>
       </c>
       <c r="S17" s="32" t="inlineStr"/>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="R21" s="31" t="inlineStr">
         <is>
-          <t>+12V DEV 15A (LOGIC BUS2-6)</t>
+          <t>+12V Dash devices +12 V (LOGIC BUS2-6)</t>
         </is>
       </c>
       <c r="S21" s="32" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="R22" s="47" t="inlineStr">
         <is>
-          <t>+12V EPSEN 7.5A (LOGIC BUS2-7)</t>
+          <t>+12V EPS enable +12 V in (LOGIC BUS2-7)</t>
         </is>
       </c>
       <c r="S22" s="48" t="inlineStr"/>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="R23" s="31" t="inlineStr">
         <is>
-          <t>+12V ACC 10A (LOGIC BUS2-8)</t>
+          <t>+12V A/C clutch +12 V in (LOGIC BUS2-8)</t>
         </is>
       </c>
       <c r="S23" s="32" t="inlineStr"/>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="R24" s="47" t="inlineStr">
         <is>
-          <t>+12V ALMIG 2A (LOGIC BUS2-9)</t>
+          <t>+12V Alarm ignition +12V (LOGIC BUS2-9)</t>
         </is>
       </c>
       <c r="S24" s="48" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R25" s="31" t="inlineStr">
         <is>
-          <t>+12V HTR 40A (POWER AMI IN-1)</t>
+          <t>+12V Heater relay feed (POWER AMI IN-1)</t>
         </is>
       </c>
       <c r="S25" s="32" t="inlineStr"/>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="R26" s="47" t="inlineStr">
         <is>
-          <t>+12V EFI 30A (POWER AMI IN-2)</t>
+          <t>+12V EFI relay feed (POWER AMI IN-2)</t>
         </is>
       </c>
       <c r="S26" s="48" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="R27" s="31" t="inlineStr">
         <is>
-          <t>+12V STR 30A (POWER AMI IN-3)</t>
+          <t>+12V Start relay feed (POWER AMI IN-3)</t>
         </is>
       </c>
       <c r="S27" s="32" t="inlineStr"/>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="R28" s="47" t="inlineStr">
         <is>
-          <t>+12V FAN 40A (POWER AMI IN-4)</t>
+          <t>+12V Rad fan relay feed (POWER AMI IN-4)</t>
         </is>
       </c>
       <c r="S28" s="48" t="inlineStr"/>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="R29" s="31" t="inlineStr">
         <is>
-          <t>+12V FAN2 30A (POWER AMI IN-5)</t>
+          <t>+12V Cond fan relay feed (POWER AMI IN-5)</t>
         </is>
       </c>
       <c r="S29" s="32" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="R30" s="47" t="inlineStr">
         <is>
-          <t>+12V PWR 30A (POWER AMI IN-6)</t>
+          <t>+12V Power relay feed (POWER AMI IN-6)</t>
         </is>
       </c>
       <c r="S30" s="48" t="inlineStr"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="R31" s="31" t="inlineStr">
         <is>
-          <t>+12V BUS1 50A (POWER AMI OUT-1)</t>
+          <t>+12V LOGIC Bus 1 feed (POWER AMI OUT-1)</t>
         </is>
       </c>
       <c r="S31" s="32" t="inlineStr"/>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="R32" s="47" t="inlineStr">
         <is>
-          <t>+12V EPS 60A (POWER AMI OUT-6)</t>
+          <t>+12V EHPS relay feed (POWER AMI OUT-6)</t>
         </is>
       </c>
       <c r="S32" s="48" t="inlineStr"/>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="R54" s="47" t="inlineStr">
         <is>
-          <t>+12V HL 15A (LOGIC BUS1-2)</t>
+          <t>+12V Head LH +12 V feed (LOGIC BUS1-2)</t>
         </is>
       </c>
       <c r="S54" s="48" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="R55" s="31" t="inlineStr">
         <is>
-          <t>+12V HL 15A (LOGIC BUS1-2)</t>
+          <t>+12V Head LH +12 V feed (LOGIC BUS1-2)</t>
         </is>
       </c>
       <c r="S55" s="32" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="R56" s="47" t="inlineStr">
         <is>
-          <t>+12V HR 15A (LOGIC BUS1-3)</t>
+          <t>+12V Head RH +12 V feed (LOGIC BUS1-3)</t>
         </is>
       </c>
       <c r="S56" s="48" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="R57" s="31" t="inlineStr">
         <is>
-          <t>+12V HR 15A (LOGIC BUS1-3)</t>
+          <t>+12V Head RH +12 V feed (LOGIC BUS1-3)</t>
         </is>
       </c>
       <c r="S57" s="32" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="R60" s="47" t="inlineStr">
         <is>
-          <t>+12V HZ 15A (LOGIC BUS1-4)</t>
+          <t>+12V Haz-horn +12 V feed (LOGIC BUS1-4)</t>
         </is>
       </c>
       <c r="S60" s="48" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="R61" s="31" t="inlineStr">
         <is>
-          <t>+12V HZ 15A (LOGIC BUS1-4)</t>
+          <t>+12V Haz-horn +12 V feed (LOGIC BUS1-4)</t>
         </is>
       </c>
       <c r="S61" s="32" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="R62" s="47" t="inlineStr">
         <is>
-          <t>+12V HZ 15A (LOGIC BUS1-4)</t>
+          <t>+12V Haz-horn +12 V feed (LOGIC BUS1-4)</t>
         </is>
       </c>
       <c r="S62" s="48" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="E6" s="47" t="inlineStr">
         <is>
-          <t>+12V HZ 15A (LOGIC BUS1-4)</t>
+          <t>+12V Haz-horn +12 V feed (LOGIC BUS1-4)</t>
         </is>
       </c>
       <c r="F6" s="48" t="n">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="E7" s="31" t="inlineStr">
         <is>
-          <t>+12V HL 15A (LOGIC BUS1-2)</t>
+          <t>+12V Head LH +12 V feed (LOGIC BUS1-2)</t>
         </is>
       </c>
       <c r="F7" s="32" t="n">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="E8" s="47" t="inlineStr">
         <is>
-          <t>+12V HR 15A (LOGIC BUS1-3)</t>
+          <t>+12V Head RH +12 V feed (LOGIC BUS1-3)</t>
         </is>
       </c>
       <c r="F8" s="48" t="n">

--- a/docs/harness/wirelist/CabinPower-wirelist.xlsx
+++ b/docs/harness/wirelist/CabinPower-wirelist.xlsx
@@ -2814,7 +2814,7 @@
       <c r="AD17" s="38" t="inlineStr"/>
       <c r="AE17" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-1 (14 AWG); DRB102 95 = section B c3 'CAN-Lambda +12V, cabin fuse F5 10A (14 AWG)'</t>
+          <t>fuse-box plan fb_logic BUS2-1 (14 AWG); DRB102 95 = loom B c95 'CAN-Lambda +12 V'</t>
         </is>
       </c>
       <c r="AF17" s="38" t="inlineStr">
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="N19" s="28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" s="29" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
       <c r="AD19" s="38" t="inlineStr"/>
       <c r="AE19" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-3 (14 AWG); DRB102 2 = section A c49 'Switched 12V - COP / ignition coil power feed, fus'</t>
+          <t>fuse-box plan fb_logic BUS2-3 (14 AWG); DRB102 1 = loom A c1 'Coil +12 V feed'</t>
         </is>
       </c>
       <c r="AF19" s="38" t="inlineStr">
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="N20" s="44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" s="45" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
       <c r="AD20" s="54" t="inlineStr"/>
       <c r="AE20" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-4 (14 AWG); DRB102 1 = section A c48 'Switched 12V - INJECTOR power feed, fuse LOGIC INJ'</t>
+          <t>fuse-box plan fb_logic BUS2-4 (14 AWG); DRB102 2 = loom A c2 'Injector +12 V feed'</t>
         </is>
       </c>
       <c r="AF20" s="54" t="inlineStr">
@@ -6538,12 +6538,12 @@
       <c r="P49" s="29" t="inlineStr"/>
       <c r="Q49" s="30" t="inlineStr">
         <is>
-          <t>DRB102.62</t>
+          <t>DRB102.77</t>
         </is>
       </c>
       <c r="R49" s="31" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in (DRB102 62)</t>
+          <t>Back-up sw +12 V in (DRB102 77)</t>
         </is>
       </c>
       <c r="S49" s="32" t="inlineStr">
@@ -8240,12 +8240,12 @@
       <c r="P63" s="29" t="inlineStr"/>
       <c r="Q63" s="30" t="inlineStr">
         <is>
-          <t>DRB102.62</t>
+          <t>DRB102.77</t>
         </is>
       </c>
       <c r="R63" s="31" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in (DRB102 62)</t>
+          <t>Back-up sw +12 V in (DRB102 77)</t>
         </is>
       </c>
       <c r="S63" s="32" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="D3" s="30" t="inlineStr">
         <is>
-          <t>DRB102.62</t>
+          <t>DRB102.77</t>
         </is>
       </c>
       <c r="E3" s="31" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in (DRB102 62)</t>
+          <t>Back-up sw +12 V in (DRB102 77)</t>
         </is>
       </c>
       <c r="F3" s="32" t="n">

--- a/docs/harness/wirelist/CabinPower-wirelist.xlsx
+++ b/docs/harness/wirelist/CabinPower-wirelist.xlsx
@@ -3638,7 +3638,7 @@
       </c>
       <c r="V24" s="50" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="W24" s="50" t="inlineStr"/>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="V37" s="34" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W37" s="34" t="inlineStr"/>
@@ -5273,11 +5273,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W38" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+      <c r="W38" s="50" t="inlineStr"/>
       <c r="X38" s="50" t="inlineStr">
         <is>
           <t>White-White</t>
@@ -5391,7 +5387,7 @@
       </c>
       <c r="V39" s="34" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W39" s="34" t="inlineStr"/>
@@ -5500,7 +5496,7 @@
       </c>
       <c r="V40" s="50" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W40" s="50" t="inlineStr"/>
@@ -5750,7 +5746,7 @@
       </c>
       <c r="V42" s="50" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W42" s="50" t="inlineStr"/>
@@ -5972,7 +5968,7 @@
       </c>
       <c r="V44" s="50" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W44" s="50" t="inlineStr"/>
@@ -6208,7 +6204,7 @@
       </c>
       <c r="V46" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W46" s="50" t="inlineStr"/>
@@ -6317,7 +6313,7 @@
       </c>
       <c r="V47" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W47" s="34" t="inlineStr"/>
@@ -6437,11 +6433,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W48" s="50" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
+      <c r="W48" s="50" t="inlineStr"/>
       <c r="X48" s="50" t="inlineStr">
         <is>
           <t>White</t>
@@ -6560,11 +6552,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W49" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W49" s="34" t="inlineStr"/>
       <c r="X49" s="34" t="inlineStr">
         <is>
           <t>White</t>
@@ -6692,7 +6680,7 @@
       </c>
       <c r="V50" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W50" s="50" t="inlineStr"/>
@@ -7083,7 +7071,7 @@
       </c>
       <c r="V53" s="34" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W53" s="34" t="inlineStr"/>
@@ -8262,11 +8250,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W63" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W63" s="34" t="inlineStr"/>
       <c r="X63" s="34" t="inlineStr">
         <is>
           <t>White</t>

--- a/docs/harness/wirelist/CabinPower-wirelist.xlsx
+++ b/docs/harness/wirelist/CabinPower-wirelist.xlsx
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="L17" s="28" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>bh_fw</t>
         </is>
       </c>
       <c r="M17" s="29" t="inlineStr">
@@ -2814,7 +2814,7 @@
       <c r="AD17" s="38" t="inlineStr"/>
       <c r="AE17" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-1 (14 AWG); DRB102 95 = loom B c95 'CAN-Lambda +12 V'</t>
+          <t>fuse-box plan fb_logic BUS2-1 (14 AWG); DRB102 95 = c95 'CAN-Lambda +12 V'</t>
         </is>
       </c>
       <c r="AF17" s="38" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AG17" s="38" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on B-cabin, 120 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="L19" s="28" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>bh_fw</t>
         </is>
       </c>
       <c r="M19" s="29" t="inlineStr">
@@ -3056,7 +3056,7 @@
       <c r="AD19" s="38" t="inlineStr"/>
       <c r="AE19" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-3 (14 AWG); DRB102 1 = loom A c1 'Coil +12 V feed'</t>
+          <t>fuse-box plan fb_logic BUS2-3 (14 AWG); DRB102 1 = c1 'Coil +12 V feed'</t>
         </is>
       </c>
       <c r="AF19" s="38" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="AG19" s="38" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_cop_pwr_ac on A-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D20" s="39" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E20" s="40" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="L20" s="44" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>bh_fw</t>
         </is>
       </c>
       <c r="M20" s="45" t="inlineStr">
@@ -3185,7 +3185,7 @@
       <c r="AD20" s="54" t="inlineStr"/>
       <c r="AE20" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-4 (14 AWG); DRB102 2 = loom A c2 'Injector +12 V feed'</t>
+          <t>fuse-box plan fb_logic BUS2-4 (14 AWG); DRB102 2 = c2 'Injector +12 V feed'</t>
         </is>
       </c>
       <c r="AF20" s="54" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AG20" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_inj_pwr_ac on A-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E34" s="40" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="AG34" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w76 on A-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w76 on ECU-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="AG37" s="38" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w81 on A-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w81 on ECU-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="D38" s="39" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E38" s="40" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="AG38" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on B-cabin, 340 mm)</t>
+          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on ECU-cabin, 340 mm)</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D50" s="39" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E50" s="40" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="AG50" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_start_in on B-cabin, 350 mm; w_start_in_cp on CabinPower, 530 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_start_in on ECU-cabin, 350 mm; w_start_in_cp on CabinPower, 530 mm)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/CabinPower-wirelist.xlsx
+++ b/docs/harness/wirelist/CabinPower-wirelist.xlsx
@@ -6080,7 +6080,7 @@
       <c r="P45" s="29" t="inlineStr"/>
       <c r="Q45" s="30" t="inlineStr">
         <is>
-          <t>GND.t_pdb_gnd_htr</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R45" s="31" t="inlineStr">
@@ -6189,7 +6189,7 @@
       <c r="P46" s="45" t="inlineStr"/>
       <c r="Q46" s="46" t="inlineStr">
         <is>
-          <t>GND.t_pdb_gnd_htr</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R46" s="47" t="inlineStr">
@@ -6298,7 +6298,7 @@
       <c r="P47" s="29" t="inlineStr"/>
       <c r="Q47" s="30" t="inlineStr">
         <is>
-          <t>GND.t_pdb_gnd_htr</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R47" s="31" t="inlineStr">

--- a/docs/harness/wirelist/CabinPower-wirelist.xlsx
+++ b/docs/harness/wirelist/CabinPower-wirelist.xlsx
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="L17" s="28" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>bh_fw</t>
         </is>
       </c>
       <c r="M17" s="29" t="inlineStr">
@@ -2814,7 +2814,7 @@
       <c r="AD17" s="38" t="inlineStr"/>
       <c r="AE17" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-1 (14 AWG); DRB102 95 = loom B c95 'CAN-Lambda +12 V'</t>
+          <t>fuse-box plan fb_logic BUS2-1 (14 AWG); DRB102 95 = c95 'CAN-Lambda +12 V'</t>
         </is>
       </c>
       <c r="AF17" s="38" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AG17" s="38" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on B-cabin, 120 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_lam12_cp on CabinPower, 250 mm; w_lam12_bc on ECU-cabin, 120 mm)</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="L19" s="28" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>bh_fw</t>
         </is>
       </c>
       <c r="M19" s="29" t="inlineStr">
@@ -3056,7 +3056,7 @@
       <c r="AD19" s="38" t="inlineStr"/>
       <c r="AE19" s="38" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-3 (14 AWG); DRB102 1 = loom A c1 'Coil +12 V feed'</t>
+          <t>fuse-box plan fb_logic BUS2-3 (14 AWG); DRB102 1 = c1 'Coil +12 V feed'</t>
         </is>
       </c>
       <c r="AF19" s="38" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="AG19" s="38" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_cop_pwr_ac on A-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_cop_pwr_ac on ECU-cabin, 180 mm; w_cop_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D20" s="39" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E20" s="40" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="L20" s="44" t="inlineStr">
         <is>
-          <t>bh_a_fw</t>
+          <t>bh_fw</t>
         </is>
       </c>
       <c r="M20" s="45" t="inlineStr">
@@ -3185,7 +3185,7 @@
       <c r="AD20" s="54" t="inlineStr"/>
       <c r="AE20" s="54" t="inlineStr">
         <is>
-          <t>fuse-box plan fb_logic BUS2-4 (14 AWG); DRB102 2 = loom A c2 'Injector +12 V feed'</t>
+          <t>fuse-box plan fb_logic BUS2-4 (14 AWG); DRB102 2 = c2 'Injector +12 V feed'</t>
         </is>
       </c>
       <c r="AF20" s="54" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="AG20" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_inj_pwr_ac on A-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_inj_pwr_ac on ECU-cabin, 180 mm; w_inj_pwr_c_ac on CabinPower, 250 mm)</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="D34" s="39" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E34" s="40" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="AG34" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w76 on A-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w76 on ECU-cabin, 370 mm; w76_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D37" s="23" t="inlineStr">
         <is>
-          <t>A-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="AG37" s="38" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w81 on A-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
+          <t>owner proposed: longer half (drawn today as w81 on ECU-cabin, 380 mm; w81_cp on CabinPower, 400 mm)</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="D38" s="39" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E38" s="40" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="AG38" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on B-cabin, 340 mm)</t>
+          <t>owner proposed: longer half (drawn today as w82_ac on CabinPower, 400 mm; w82 on ECU-cabin, 340 mm)</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6080,7 @@
       <c r="P45" s="29" t="inlineStr"/>
       <c r="Q45" s="30" t="inlineStr">
         <is>
-          <t>GND.t_pdb_gnd_htr</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R45" s="31" t="inlineStr">
@@ -6189,7 +6189,7 @@
       <c r="P46" s="45" t="inlineStr"/>
       <c r="Q46" s="46" t="inlineStr">
         <is>
-          <t>GND.t_pdb_gnd_htr</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R46" s="47" t="inlineStr">
@@ -6298,7 +6298,7 @@
       <c r="P47" s="29" t="inlineStr"/>
       <c r="Q47" s="30" t="inlineStr">
         <is>
-          <t>GND.t_pdb_gnd_htr</t>
+          <t>GND.t_cluster_gnd</t>
         </is>
       </c>
       <c r="R47" s="31" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D50" s="39" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="E50" s="40" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="AG50" s="54" t="inlineStr">
         <is>
-          <t>owner proposed: longer half (drawn today as w_start_in on B-cabin, 350 mm; w_start_in_cp on CabinPower, 530 mm)</t>
+          <t>owner proposed: longer half (drawn today as w_start_in on ECU-cabin, 350 mm; w_start_in_cp on CabinPower, 530 mm)</t>
         </is>
       </c>
     </row>
